--- a/2026/GENERAL PAZ 138/Julio/Julio GRAL PAZ 138.xlsx
+++ b/2026/GENERAL PAZ 138/Julio/Julio GRAL PAZ 138.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GENERAL PAZ 138\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GENERAL PAZ 138\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F5DDEB5-22A2-4390-BE11-3CDB45A5902D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{317A577E-561C-4FE5-9E4D-3FBDD29A5A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$90</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -270,9 +275,6 @@
     <t>AYSA - NºCliente 3371074</t>
   </si>
   <si>
-    <t>TRANSFERIR A  : carolina.rc.adm - CVU: 0000003100054616492658</t>
-  </si>
-  <si>
     <t>TELEFONO : 11-5320-2676 - MAIL: consorciosrc13@gmail.com - OFICINA CON CITA PREVIA - DR MELO 2958 8° PISO</t>
   </si>
   <si>
@@ -319,6 +321,9 @@
   </si>
   <si>
     <t>Transf 24/07</t>
+  </si>
+  <si>
+    <t>TRANSFERIR A  : Cuenta SANTANDER  533-033257/4 CBU :  0720533020000003325740 - CUIT: 30-71953248-5</t>
   </si>
 </sst>
 </file>
@@ -1519,9 +1524,8 @@
     <xf numFmtId="44" fontId="8" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="44" fontId="41" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="41" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1546,6 +1550,18 @@
     <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1561,9 +1577,6 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1594,17 +1607,9 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="41" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="41" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{E13FD6FD-4381-40A3-9669-15D4AFB54255}"/>
@@ -1714,9 +1719,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1754,9 +1759,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1789,9 +1794,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1824,9 +1846,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2001,16 +2040,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L90"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2023,81 +2062,81 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="70" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B2" s="70"/>
       <c r="C2" s="70"/>
       <c r="D2" s="70"/>
     </row>
-    <row r="3" spans="1:4" ht="16.95" customHeight="1">
+    <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1">
       <c r="A3" s="70"/>
       <c r="B3" s="70"/>
       <c r="C3" s="70"/>
       <c r="D3" s="70"/>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1">
-      <c r="A4" s="144" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" s="144"/>
+      <c r="A4" s="173" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="173"/>
       <c r="C4" s="71"/>
       <c r="D4" s="71"/>
     </row>
-    <row r="5" spans="1:4" hidden="1">
-      <c r="A5" s="144"/>
-      <c r="B5" s="144"/>
+    <row r="5" spans="1:4" ht="15" hidden="1" customHeight="1">
+      <c r="A5" s="173"/>
+      <c r="B5" s="173"/>
       <c r="C5" s="71"/>
       <c r="D5" s="71"/>
     </row>
-    <row r="6" spans="1:4" hidden="1">
-      <c r="A6" s="144"/>
-      <c r="B6" s="144"/>
+    <row r="6" spans="1:4" ht="15" hidden="1" customHeight="1">
+      <c r="A6" s="173"/>
+      <c r="B6" s="173"/>
       <c r="C6" s="71"/>
       <c r="D6" s="71"/>
     </row>
     <row r="7" spans="1:4" ht="13.5" customHeight="1">
-      <c r="A7" s="144"/>
-      <c r="B7" s="144"/>
+      <c r="A7" s="173"/>
+      <c r="B7" s="173"/>
       <c r="C7" s="71"/>
       <c r="D7" s="71"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="B9" s="152" t="s">
-        <v>95</v>
+      <c r="B9" s="153" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="B10" s="152"/>
+      <c r="B10" s="153"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="152"/>
+      <c r="B11" s="153"/>
     </row>
     <row r="13" spans="1:4" hidden="1"/>
     <row r="14" spans="1:4" ht="15" customHeight="1">
-      <c r="A14" s="147" t="s">
+      <c r="A14" s="148" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="147"/>
-      <c r="C14" s="147"/>
-      <c r="D14" s="147"/>
+      <c r="B14" s="148"/>
+      <c r="C14" s="148"/>
+      <c r="D14" s="148"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
-      <c r="A15" s="147"/>
-      <c r="B15" s="147"/>
-      <c r="C15" s="147"/>
-      <c r="D15" s="147"/>
+      <c r="A15" s="148"/>
+      <c r="B15" s="148"/>
+      <c r="C15" s="148"/>
+      <c r="D15" s="148"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
-      <c r="A16" s="147"/>
-      <c r="B16" s="147"/>
-      <c r="C16" s="147"/>
-      <c r="D16" s="147"/>
+      <c r="A16" s="148"/>
+      <c r="B16" s="148"/>
+      <c r="C16" s="148"/>
+      <c r="D16" s="148"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1">
-      <c r="A17" s="147"/>
-      <c r="B17" s="147"/>
-      <c r="C17" s="147"/>
-      <c r="D17" s="147"/>
+      <c r="A17" s="148"/>
+      <c r="B17" s="148"/>
+      <c r="C17" s="148"/>
+      <c r="D17" s="148"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
       <c r="A18" s="60"/>
@@ -2105,13 +2144,13 @@
       <c r="C18" s="60"/>
       <c r="D18" s="60"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1">
       <c r="A19" s="142"/>
       <c r="B19" s="60"/>
       <c r="C19" s="60"/>
       <c r="D19" s="60"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1">
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1">
       <c r="A20" s="60"/>
       <c r="B20" s="60"/>
       <c r="C20" s="60"/>
@@ -2212,7 +2251,7 @@
     </row>
     <row r="32" spans="1:7" ht="22.5" customHeight="1">
       <c r="A32" s="96" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B32" s="114"/>
       <c r="C32" s="82">
@@ -2222,7 +2261,7 @@
       <c r="F32" s="16"/>
       <c r="G32" s="4"/>
     </row>
-    <row r="33" spans="1:6" ht="15" thickBot="1">
+    <row r="33" spans="1:6" ht="15.75" thickBot="1">
       <c r="A33" s="9" t="s">
         <v>26</v>
       </c>
@@ -2242,18 +2281,18 @@
       <c r="D34" s="26"/>
     </row>
     <row r="35" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A35" s="145" t="s">
+      <c r="A35" s="146" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" s="147"/>
+      <c r="C35" s="144">
+        <v>87914</v>
+      </c>
+      <c r="D35" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="B35" s="146"/>
-      <c r="C35" s="172">
-        <v>87914</v>
-      </c>
-      <c r="D35" s="80" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="15" thickBot="1">
+    </row>
+    <row r="36" spans="1:6" ht="15.75" thickBot="1">
       <c r="A36" s="9" t="s">
         <v>1</v>
       </c>
@@ -2334,14 +2373,14 @@
     </row>
     <row r="44" spans="1:6" ht="14.25" customHeight="1">
       <c r="A44" s="60" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B44" s="46"/>
       <c r="C44" s="85">
         <v>36019.040000000001</v>
       </c>
       <c r="D44" s="78" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="14.25" customHeight="1">
@@ -2349,14 +2388,14 @@
         <v>80</v>
       </c>
       <c r="B45" s="46"/>
-      <c r="C45" s="173">
+      <c r="C45" s="145">
         <v>207143.7</v>
       </c>
       <c r="D45" s="78" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15" thickBot="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" thickBot="1">
       <c r="A46" s="9" t="s">
         <v>3</v>
       </c>
@@ -2367,7 +2406,7 @@
         <v>243162.74000000002</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="15" thickBot="1">
+    <row r="47" spans="1:6" ht="15.75" thickBot="1">
       <c r="A47" s="8" t="s">
         <v>28</v>
       </c>
@@ -2375,17 +2414,17 @@
       <c r="C47" s="13"/>
       <c r="D47" s="53"/>
     </row>
-    <row r="48" spans="1:6" ht="19.95" customHeight="1">
-      <c r="A48" s="145" t="s">
-        <v>94</v>
-      </c>
-      <c r="B48" s="146"/>
+    <row r="48" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A48" s="146" t="s">
+        <v>93</v>
+      </c>
+      <c r="B48" s="147"/>
       <c r="C48" s="85">
         <v>150000</v>
       </c>
       <c r="D48" s="76"/>
     </row>
-    <row r="49" spans="1:6" ht="15" thickBot="1">
+    <row r="49" spans="1:6" ht="15.75" thickBot="1">
       <c r="A49" s="9" t="s">
         <v>11</v>
       </c>
@@ -2396,7 +2435,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15" thickBot="1">
+    <row r="50" spans="1:6" ht="15.75" thickBot="1">
       <c r="A50" s="8" t="s">
         <v>21</v>
       </c>
@@ -2410,7 +2449,7 @@
       <c r="C51" s="87"/>
       <c r="D51" s="56"/>
     </row>
-    <row r="52" spans="1:6" ht="15" thickBot="1">
+    <row r="52" spans="1:6" ht="15.75" thickBot="1">
       <c r="A52" s="117" t="s">
         <v>26</v>
       </c>
@@ -2421,30 +2460,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1">
+    <row r="53" spans="1:6" ht="15.75" thickBot="1">
       <c r="A53" s="46"/>
       <c r="B53" s="46"/>
       <c r="C53" s="46"/>
       <c r="D53" s="58"/>
     </row>
     <row r="54" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A54" s="149" t="s">
+      <c r="A54" s="150" t="s">
         <v>75</v>
       </c>
-      <c r="B54" s="150"/>
-      <c r="C54" s="151"/>
+      <c r="B54" s="151"/>
+      <c r="C54" s="152"/>
       <c r="D54" s="59">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15" thickBot="1">
+    <row r="55" spans="1:6" ht="15.75" thickBot="1">
       <c r="A55" s="118"/>
       <c r="B55" s="60"/>
       <c r="C55" s="60"/>
       <c r="D55" s="61"/>
       <c r="E55" s="17"/>
     </row>
-    <row r="56" spans="1:6" ht="15" thickBot="1">
+    <row r="56" spans="1:6" ht="15.75" thickBot="1">
       <c r="A56" s="119" t="s">
         <v>22</v>
       </c>
@@ -2464,7 +2503,7 @@
       <c r="D57" s="60"/>
       <c r="F57" s="75"/>
     </row>
-    <row r="58" spans="1:6" ht="15" thickBot="1">
+    <row r="58" spans="1:6" ht="15.75" thickBot="1">
       <c r="A58" s="60"/>
       <c r="B58" s="60"/>
       <c r="C58" s="60"/>
@@ -2479,14 +2518,14 @@
       <c r="D59" s="65"/>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="145"/>
-      <c r="B60" s="146"/>
+      <c r="A60" s="146"/>
+      <c r="B60" s="147"/>
       <c r="C60" s="85"/>
       <c r="D60" s="76"/>
     </row>
     <row r="61" spans="1:6">
-      <c r="A61" s="145"/>
-      <c r="B61" s="146"/>
+      <c r="A61" s="146"/>
+      <c r="B61" s="147"/>
       <c r="C61" s="85"/>
       <c r="D61" s="52"/>
     </row>
@@ -2527,13 +2566,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="15" thickBot="1">
+    <row r="67" spans="1:4" ht="15.75" thickBot="1">
       <c r="A67" s="60"/>
       <c r="B67" s="60"/>
       <c r="C67" s="60"/>
       <c r="D67" s="60"/>
     </row>
-    <row r="68" spans="1:4" ht="15" thickBot="1">
+    <row r="68" spans="1:4" ht="15.75" thickBot="1">
       <c r="A68" s="119" t="s">
         <v>33</v>
       </c>
@@ -2544,13 +2583,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="15" thickBot="1">
+    <row r="69" spans="1:4" ht="15.75" thickBot="1">
       <c r="A69" s="60"/>
       <c r="B69" s="60"/>
       <c r="C69" s="60"/>
       <c r="D69" s="60"/>
     </row>
-    <row r="70" spans="1:4" ht="15" thickBot="1">
+    <row r="70" spans="1:4" ht="15.75" thickBot="1">
       <c r="A70" s="132" t="s">
         <v>23</v>
       </c>
@@ -2561,7 +2600,7 @@
       <c r="C70" s="134"/>
       <c r="D70" s="60"/>
     </row>
-    <row r="71" spans="1:4" ht="15" thickBot="1">
+    <row r="71" spans="1:4" ht="15.75" thickBot="1">
       <c r="A71" s="132" t="s">
         <v>24</v>
       </c>
@@ -2572,7 +2611,7 @@
       <c r="C71" s="60"/>
       <c r="D71" s="60"/>
     </row>
-    <row r="72" spans="1:4" ht="15" thickBot="1">
+    <row r="72" spans="1:4" ht="15.75" thickBot="1">
       <c r="A72" s="132" t="s">
         <v>34</v>
       </c>
@@ -2583,7 +2622,7 @@
       <c r="C72" s="60"/>
       <c r="D72" s="60"/>
     </row>
-    <row r="73" spans="1:4" ht="15" thickBot="1">
+    <row r="73" spans="1:4" ht="15.75" thickBot="1">
       <c r="A73" s="132" t="s">
         <v>49</v>
       </c>
@@ -2612,7 +2651,7 @@
       <c r="C76" s="60"/>
       <c r="D76" s="60"/>
     </row>
-    <row r="77" spans="1:4" ht="15" thickBot="1">
+    <row r="77" spans="1:4" ht="15.75" thickBot="1">
       <c r="A77" s="135" t="s">
         <v>44</v>
       </c>
@@ -2685,14 +2724,14 @@
       <c r="D84" s="124"/>
     </row>
     <row r="85" spans="1:12">
-      <c r="A85" s="148" t="s">
+      <c r="A85" s="149" t="s">
         <v>43</v>
       </c>
-      <c r="B85" s="148"/>
+      <c r="B85" s="149"/>
     </row>
     <row r="86" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A86" s="148"/>
-      <c r="B86" s="148"/>
+      <c r="A86" s="149"/>
+      <c r="B86" s="149"/>
     </row>
     <row r="87" spans="1:12" ht="32.25" customHeight="1">
       <c r="A87" s="66"/>
@@ -2735,45 +2774,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="12.9" customHeight="1">
+    <row r="1" spans="1:21" ht="12.95" customHeight="1">
       <c r="A1" s="98"/>
-      <c r="B1" s="153" t="str">
+      <c r="B1" s="158" t="str">
         <f>RESUMEN!A4</f>
-        <v>TRANSFERIR A  : carolina.rc.adm - CVU: 0000003100054616492658</v>
-      </c>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
-      <c r="G1" s="153"/>
-      <c r="H1" s="153"/>
-      <c r="I1" s="153"/>
-      <c r="J1" s="153"/>
-      <c r="K1" s="153"/>
+        <v>TRANSFERIR A  : Cuenta SANTANDER  533-033257/4 CBU :  0720533020000003325740 - CUIT: 30-71953248-5</v>
+      </c>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
       <c r="L1" s="99"/>
       <c r="M1" s="99"/>
       <c r="N1" s="99"/>
@@ -2782,16 +2821,16 @@
     </row>
     <row r="2" spans="1:21" ht="14.25" customHeight="1">
       <c r="A2" s="101"/>
-      <c r="B2" s="154"/>
-      <c r="C2" s="154"/>
-      <c r="D2" s="154"/>
-      <c r="E2" s="154"/>
-      <c r="F2" s="154"/>
-      <c r="G2" s="154"/>
-      <c r="H2" s="154"/>
-      <c r="I2" s="154"/>
-      <c r="J2" s="154"/>
-      <c r="K2" s="154"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
       <c r="L2" s="102"/>
       <c r="M2" s="102" t="s">
         <v>4</v>
@@ -2808,16 +2847,16 @@
     </row>
     <row r="3" spans="1:21" ht="16.5" customHeight="1" thickBot="1">
       <c r="A3" s="104"/>
-      <c r="B3" s="155"/>
-      <c r="C3" s="155"/>
-      <c r="D3" s="155"/>
-      <c r="E3" s="155"/>
-      <c r="F3" s="155"/>
-      <c r="G3" s="155"/>
-      <c r="H3" s="155"/>
-      <c r="I3" s="155"/>
-      <c r="J3" s="155"/>
-      <c r="K3" s="155"/>
+      <c r="B3" s="160"/>
+      <c r="C3" s="160"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="160"/>
       <c r="L3" s="105"/>
       <c r="M3" s="105" t="s">
         <v>53</v>
@@ -2830,96 +2869,96 @@
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="166" t="s">
+      <c r="B4" s="170" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="167"/>
-      <c r="G4" s="167"/>
-      <c r="H4" s="167"/>
-      <c r="I4" s="167"/>
-      <c r="J4" s="167"/>
-      <c r="K4" s="167"/>
-      <c r="L4" s="167"/>
-      <c r="M4" s="167"/>
-      <c r="N4" s="167"/>
-      <c r="O4" s="167"/>
-      <c r="P4" s="168"/>
+      <c r="C4" s="171"/>
+      <c r="D4" s="171"/>
+      <c r="E4" s="171"/>
+      <c r="F4" s="171"/>
+      <c r="G4" s="171"/>
+      <c r="H4" s="171"/>
+      <c r="I4" s="171"/>
+      <c r="J4" s="171"/>
+      <c r="K4" s="171"/>
+      <c r="L4" s="171"/>
+      <c r="M4" s="171"/>
+      <c r="N4" s="171"/>
+      <c r="O4" s="171"/>
+      <c r="P4" s="172"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="154" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="171" t="s">
+      <c r="B5" s="156" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="158" t="s">
+      <c r="C5" s="157" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="158" t="s">
+      <c r="D5" s="157" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="158" t="s">
+      <c r="E5" s="157" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="158" t="s">
+      <c r="F5" s="157" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="158" t="s">
+      <c r="G5" s="157" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="158" t="s">
+      <c r="H5" s="157" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="158" t="s">
+      <c r="I5" s="157" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="162" t="s">
+      <c r="J5" s="166" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="160" t="s">
+      <c r="K5" s="164" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="160" t="s">
+      <c r="L5" s="164" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="160" t="s">
+      <c r="M5" s="164" t="s">
         <v>37</v>
       </c>
-      <c r="N5" s="164" t="s">
+      <c r="N5" s="168" t="s">
         <v>48</v>
       </c>
       <c r="O5" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="P5" s="156" t="s">
+      <c r="P5" s="161" t="s">
         <v>46</v>
       </c>
       <c r="S5" s="17"/>
       <c r="T5" s="16"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="170"/>
-      <c r="B6" s="171"/>
-      <c r="C6" s="158"/>
-      <c r="D6" s="158"/>
-      <c r="E6" s="159"/>
-      <c r="F6" s="158"/>
-      <c r="G6" s="158"/>
-      <c r="H6" s="158"/>
-      <c r="I6" s="159"/>
-      <c r="J6" s="163"/>
-      <c r="K6" s="161"/>
-      <c r="L6" s="160"/>
-      <c r="M6" s="161"/>
-      <c r="N6" s="165"/>
+      <c r="A6" s="155"/>
+      <c r="B6" s="156"/>
+      <c r="C6" s="157"/>
+      <c r="D6" s="157"/>
+      <c r="E6" s="163"/>
+      <c r="F6" s="157"/>
+      <c r="G6" s="157"/>
+      <c r="H6" s="157"/>
+      <c r="I6" s="163"/>
+      <c r="J6" s="167"/>
+      <c r="K6" s="165"/>
+      <c r="L6" s="164"/>
+      <c r="M6" s="165"/>
+      <c r="N6" s="169"/>
       <c r="O6" s="22" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 17/08</v>
       </c>
-      <c r="P6" s="156"/>
+      <c r="P6" s="161"/>
       <c r="S6" s="16">
         <v>65160</v>
       </c>
@@ -2942,7 +2981,7 @@
         <v>61</v>
       </c>
       <c r="D7" s="77" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E7" s="77"/>
       <c r="F7" s="90">
@@ -3206,7 +3245,7 @@
         <v>65</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E11" s="25"/>
       <c r="F11" s="27">
@@ -3273,7 +3312,7 @@
         <v>66</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E12" s="24"/>
       <c r="F12" s="27">
@@ -3340,7 +3379,7 @@
         <v>67</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E13" s="24"/>
       <c r="F13" s="90">
@@ -3411,7 +3450,7 @@
         <v>79</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F14" s="90">
         <v>8.9</v>
@@ -3479,7 +3518,7 @@
         <v>79</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F15" s="27">
         <v>11.2</v>
@@ -3532,7 +3571,7 @@
         <v>141245</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="16.2" customHeight="1">
+    <row r="16" spans="1:21" ht="16.149999999999999" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
@@ -3543,7 +3582,7 @@
         <v>70</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E16" s="89"/>
       <c r="F16" s="27">
@@ -3598,7 +3637,7 @@
         <v>243540</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15" thickBot="1">
+    <row r="17" spans="1:17" ht="15.75" thickBot="1">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -3632,7 +3671,7 @@
       <c r="P17" s="35"/>
       <c r="Q17" s="17"/>
     </row>
-    <row r="18" spans="1:17" ht="15" thickBot="1">
+    <row r="18" spans="1:17" ht="15.75" thickBot="1">
       <c r="B18" s="41"/>
       <c r="C18" s="42"/>
       <c r="D18" s="43"/>
@@ -3681,98 +3720,93 @@
       <c r="E19" s="19"/>
     </row>
     <row r="21" spans="1:17">
-      <c r="D21" s="157" t="s">
+      <c r="D21" s="162" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="157"/>
-      <c r="F21" s="157"/>
-      <c r="G21" s="157"/>
-      <c r="H21" s="157"/>
-      <c r="I21" s="157"/>
-      <c r="J21" s="157"/>
-      <c r="K21" s="157"/>
-      <c r="L21" s="157"/>
-      <c r="M21" s="157"/>
-      <c r="N21" s="157"/>
-      <c r="O21" s="157"/>
+      <c r="E21" s="162"/>
+      <c r="F21" s="162"/>
+      <c r="G21" s="162"/>
+      <c r="H21" s="162"/>
+      <c r="I21" s="162"/>
+      <c r="J21" s="162"/>
+      <c r="K21" s="162"/>
+      <c r="L21" s="162"/>
+      <c r="M21" s="162"/>
+      <c r="N21" s="162"/>
+      <c r="O21" s="162"/>
     </row>
     <row r="22" spans="1:17">
-      <c r="D22" s="157"/>
-      <c r="E22" s="157"/>
-      <c r="F22" s="157"/>
-      <c r="G22" s="157"/>
-      <c r="H22" s="157"/>
-      <c r="I22" s="157"/>
-      <c r="J22" s="157"/>
-      <c r="K22" s="157"/>
-      <c r="L22" s="157"/>
-      <c r="M22" s="157"/>
-      <c r="N22" s="157"/>
-      <c r="O22" s="157"/>
+      <c r="D22" s="162"/>
+      <c r="E22" s="162"/>
+      <c r="F22" s="162"/>
+      <c r="G22" s="162"/>
+      <c r="H22" s="162"/>
+      <c r="I22" s="162"/>
+      <c r="J22" s="162"/>
+      <c r="K22" s="162"/>
+      <c r="L22" s="162"/>
+      <c r="M22" s="162"/>
+      <c r="N22" s="162"/>
+      <c r="O22" s="162"/>
     </row>
     <row r="23" spans="1:17">
-      <c r="D23" s="157"/>
-      <c r="E23" s="157"/>
-      <c r="F23" s="157"/>
-      <c r="G23" s="157"/>
-      <c r="H23" s="157"/>
-      <c r="I23" s="157"/>
-      <c r="J23" s="157"/>
-      <c r="K23" s="157"/>
-      <c r="L23" s="157"/>
-      <c r="M23" s="157"/>
-      <c r="N23" s="157"/>
-      <c r="O23" s="157"/>
+      <c r="D23" s="162"/>
+      <c r="E23" s="162"/>
+      <c r="F23" s="162"/>
+      <c r="G23" s="162"/>
+      <c r="H23" s="162"/>
+      <c r="I23" s="162"/>
+      <c r="J23" s="162"/>
+      <c r="K23" s="162"/>
+      <c r="L23" s="162"/>
+      <c r="M23" s="162"/>
+      <c r="N23" s="162"/>
+      <c r="O23" s="162"/>
     </row>
     <row r="24" spans="1:17">
-      <c r="D24" s="157"/>
-      <c r="E24" s="157"/>
-      <c r="F24" s="157"/>
-      <c r="G24" s="157"/>
-      <c r="H24" s="157"/>
-      <c r="I24" s="157"/>
-      <c r="J24" s="157"/>
-      <c r="K24" s="157"/>
-      <c r="L24" s="157"/>
-      <c r="M24" s="157"/>
-      <c r="N24" s="157"/>
-      <c r="O24" s="157"/>
+      <c r="D24" s="162"/>
+      <c r="E24" s="162"/>
+      <c r="F24" s="162"/>
+      <c r="G24" s="162"/>
+      <c r="H24" s="162"/>
+      <c r="I24" s="162"/>
+      <c r="J24" s="162"/>
+      <c r="K24" s="162"/>
+      <c r="L24" s="162"/>
+      <c r="M24" s="162"/>
+      <c r="N24" s="162"/>
+      <c r="O24" s="162"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="D25" s="157"/>
-      <c r="E25" s="157"/>
-      <c r="F25" s="157"/>
-      <c r="G25" s="157"/>
-      <c r="H25" s="157"/>
-      <c r="I25" s="157"/>
-      <c r="J25" s="157"/>
-      <c r="K25" s="157"/>
-      <c r="L25" s="157"/>
-      <c r="M25" s="157"/>
-      <c r="N25" s="157"/>
-      <c r="O25" s="157"/>
+      <c r="D25" s="162"/>
+      <c r="E25" s="162"/>
+      <c r="F25" s="162"/>
+      <c r="G25" s="162"/>
+      <c r="H25" s="162"/>
+      <c r="I25" s="162"/>
+      <c r="J25" s="162"/>
+      <c r="K25" s="162"/>
+      <c r="L25" s="162"/>
+      <c r="M25" s="162"/>
+      <c r="N25" s="162"/>
+      <c r="O25" s="162"/>
     </row>
     <row r="26" spans="1:17" ht="65.25" customHeight="1">
-      <c r="D26" s="157"/>
-      <c r="E26" s="157"/>
-      <c r="F26" s="157"/>
-      <c r="G26" s="157"/>
-      <c r="H26" s="157"/>
-      <c r="I26" s="157"/>
-      <c r="J26" s="157"/>
-      <c r="K26" s="157"/>
-      <c r="L26" s="157"/>
-      <c r="M26" s="157"/>
-      <c r="N26" s="157"/>
-      <c r="O26" s="157"/>
+      <c r="D26" s="162"/>
+      <c r="E26" s="162"/>
+      <c r="F26" s="162"/>
+      <c r="G26" s="162"/>
+      <c r="H26" s="162"/>
+      <c r="I26" s="162"/>
+      <c r="J26" s="162"/>
+      <c r="K26" s="162"/>
+      <c r="L26" s="162"/>
+      <c r="M26" s="162"/>
+      <c r="N26" s="162"/>
+      <c r="O26" s="162"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="D21:O26"/>
@@ -3786,6 +3820,11 @@
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="B4:P4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>
